--- a/Tables/BALANCE_PARAM_DATA.xlsx
+++ b/Tables/BALANCE_PARAM_DATA.xlsx
@@ -830,12 +830,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">slot</t>
+          <t xml:space="preserve">dBAoe</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">동시 출격 슬롯</t>
+          <t xml:space="preserve">드론 기당피해 — 광역형</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -844,24 +844,24 @@
         </is>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">상수(강화 비대상 — 미결 #13)</t>
+          <t xml:space="preserve">✅ **무기 스펙트럼 좌표**(플레이어블 로봇 기획서 · 2026-07-17·07-23 확정 · 「광역형 50×2.0」). 2026-09-19 에 `droneAoeDamageFactor` 0.5 를 폐기하고 이 좌표로 모았다(`260918_W02` 5장 문안) — 종전에는 같은 값이 **문서에 50, 코드에 0.5** 로 두 자리에 살았다. ⚠️ **감쇠 규칙이 아니다** — 충전량·수명과는 다른 축이고, 「표적당 절반」은 이 좌표가 누적형 100 의 절반이라는 사실의 다른 표현일 뿐이다</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">방출 병렬도</t>
+          <t xml:space="preserve">광역형의 대가를 좌표 하나로 적는다 — 배수는 이 수를 누적형 100 으로 나눠 나온다</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">07 3장 · 밸런스 #13</t>
+          <t xml:space="preserve">260918_W02 5장 · 플레이어블 로봇 기획서「무기 스펙트럼」</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">r</t>
+          <t xml:space="preserve">slot</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">방출률 r(기/초/슬롯)</t>
+          <t xml:space="preserve">동시 출격 슬롯</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -888,24 +888,24 @@
         </is>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">min(유입 1.0, 슬롯 3×r 1.0)=1.0 실측</t>
+          <t xml:space="preserve">상수(강화 비대상 — 미결 #13)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">min(유입,슬롯×r)</t>
+          <t xml:space="preserve">방출 병렬도</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 10-3 (2026-07-23)</t>
+          <t xml:space="preserve">07 3장 · 밸런스 #13</t>
         </is>
       </c>
     </row>
@@ -918,38 +918,38 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">pw</t>
+          <t xml:space="preserve">r</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">노드 전력 소비(합)</t>
+          <t xml:space="preserve">방출률 r(기/초/슬롯)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">병목</t>
+          <t xml:space="preserve">로봇B 드론</t>
         </is>
       </c>
       <c r="F21">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">가동 고정비(TBD — 노드 카탈로그와 결합)</t>
+          <t xml:space="preserve">min(유입 1.0, 슬롯 3×r 1.0)=1.0 실측</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">전력=고정비 전용</t>
+          <t xml:space="preserve">min(유입,슬롯×r)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 1장</t>
+          <t xml:space="preserve">밸런스 10-3 (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">pwc</t>
+          <t xml:space="preserve">pw</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">전력 공급 용량</t>
+          <t xml:space="preserve">노드 전력 소비(합)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -976,24 +976,24 @@
         </is>
       </c>
       <c r="F22">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">발전 용량(TBD)</t>
+          <t xml:space="preserve">가동 고정비(TBD — 노드 카탈로그와 결합)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">pwc&lt;pw면 효율&lt;1</t>
+          <t xml:space="preserve">전력=고정비 전용</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 10-3</t>
+          <t xml:space="preserve">밸런스 1장</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">belt</t>
+          <t xml:space="preserve">pwc</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">벨트 용량(처리량/초)</t>
+          <t xml:space="preserve">전력 공급 용량</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1020,24 +1020,24 @@
         </is>
       </c>
       <c r="F23">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">벨트 대역(TBD)</t>
+          <t xml:space="preserve">발전 용량(TBD)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">필요&lt;용량이면 무손실</t>
+          <t xml:space="preserve">pwc&lt;pw면 효율&lt;1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 6-1</t>
+          <t xml:space="preserve">밸런스 10-3</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">heat</t>
+          <t xml:space="preserve">belt</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">발열 발생/초</t>
+          <t xml:space="preserve">벨트 용량(처리량/초)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1064,19 +1064,19 @@
         </is>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">발열 합(TBD)</t>
+          <t xml:space="preserve">벨트 대역(TBD)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">임계 초과 시 감쇠</t>
+          <t xml:space="preserve">필요&lt;용량이면 무손실</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">heatc</t>
+          <t xml:space="preserve">heat</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">발열 임계</t>
+          <t xml:space="preserve">발열 발생/초</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1108,19 +1108,19 @@
         </is>
       </c>
       <c r="F25">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">냉각 임계(TBD)</t>
+          <t xml:space="preserve">발열 합(TBD)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">heat&gt;heatc면 감쇠</t>
+          <t xml:space="preserve">임계 초과 시 감쇠</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1138,38 +1138,38 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">store</t>
+          <t xml:space="preserve">heatc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">저장 용량(태그 만충)</t>
+          <t xml:space="preserve">발열 임계</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">태그</t>
+          <t xml:space="preserve">병목</t>
         </is>
       </c>
       <c r="F26">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">태그 주기 10초(÷대표 생산 4발/초) · 교대 계수 0.96</t>
+          <t xml:space="preserve">냉각 임계(TBD)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">태그 주기 결정</t>
+          <t xml:space="preserve">heat&gt;heatc면 감쇠</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 4장 (2026-07-23)</t>
+          <t xml:space="preserve">밸런스 6-1</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagspec</t>
+          <t xml:space="preserve">store</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">등장 특공(마진항)</t>
+          <t xml:space="preserve">저장 용량(태그 만충)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F27">
-        <v>2103</v>
+        <v>40</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">식 확정: 비축 발수 × 강화 평균 발당피해 = 40×52.6</t>
+          <t xml:space="preserve">태그 주기 10초(÷대표 생산 4발/초) · 교대 계수 0.96</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">요구치 예산 밖 마진</t>
+          <t xml:space="preserve">태그 주기 결정</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1226,38 +1226,38 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">mergeMult</t>
+          <t xml:space="preserve">tagspec</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체 배율</t>
+          <t xml:space="preserve">등장 특공(마진항)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체·버스트</t>
+          <t xml:space="preserve">태그</t>
         </is>
       </c>
       <c r="F28">
-        <v>1.8</v>
+        <v>2103</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">변신 화력 = (A+B 원 DPS) × 배율 — 교대 공백 미적용</t>
+          <t xml:space="preserve">식 확정: 비축 발수 × 강화 평균 발당피해 = 40×52.6</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">예산 안 지속 항 (배율=키우기 축, 밑=물류 축)</t>
+          <t xml:space="preserve">요구치 예산 밖 마진</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 5-2 (2026-07-23)</t>
+          <t xml:space="preserve">밸런스 4장 (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">mergeOutputMult</t>
+          <t xml:space="preserve">mergeMult</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체 산출량 배율</t>
+          <t xml:space="preserve">합체 배율</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1284,24 +1284,24 @@
         </is>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체 지속 중 두 보드 모든 노드의 산출량 ×2 — 재료·전력·생산 주기는 그대로, 벨트는 제외(12/초 고정). 구 표기 「생산량 200%」와 같은 값이다</t>
+          <t xml:space="preserve">변신 화력 = (A+B 원 DPS) × 배율 — 교대 공백 미적용</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체 예외 — 극적인 효과 + 두 마운트를 비우지 않게 받치는 장치</t>
+          <t xml:space="preserve">예산 안 지속 항 (배율=키우기 축, 밑=물류 축)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스「밸런스 확정 원칙」합체 예외 · 260917_W03 5장·7-2</t>
+          <t xml:space="preserve">밸런스 5-2 (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeStacksPerBooster</t>
+          <t xml:space="preserve">mergeOutputMult</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">부스터 1대당 회피 스택 칸</t>
+          <t xml:space="preserve">합체 산출량 배율</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1328,24 +1328,24 @@
         </is>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">회피 스택 상한 = 부스터 노드 대수 × 이 계수. 구 2칸 → 4칸(2026-09-17 사용자 확정) — 260917_V02 2-2 실측에서 상한 4가 필요치 50부터 이미 병목이었다. 시작 보드(부스터 둘) 상한 8</t>
+          <t xml:space="preserve">합체 지속 중 두 보드 모든 노드의 산출량 ×2 — 재료·전력·생산 주기는 그대로, 벨트는 제외(12/초 고정). 구 표기 「생산량 200%」와 같은 값이다</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">로봇 생존 손잡이 — 그릇 쪽. 채우는 속도(추진제 필요 생산치)와 다른 축이다</t>
+          <t xml:space="preserve">합체 예외 — 극적인 효과 + 두 마운트를 비우지 않게 받치는 장치</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스「회피와 기동 라인」· 전투「회피」· 260917_W04 2장</t>
+          <t xml:space="preserve">밸런스「밸런스 확정 원칙」합체 예외 · 260917_W03 5장·7-2</t>
         </is>
       </c>
     </row>
@@ -1358,38 +1358,38 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">droneAoeDamageFactor</t>
+          <t xml:space="preserve">dodgeStacksPerBooster</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">광역형 드론 표적당 피해 비</t>
+          <t xml:space="preserve">부스터 1대당 회피 스택 칸</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">원점·곡선</t>
+          <t xml:space="preserve">합체·버스트</t>
         </is>
       </c>
       <c r="F31">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ **가정 표기** — 사용자가 「문서대로 코드를 절반으로」로 닫았고(2026-09-18), 수는 `260918_W01` 3-1 표의 **표적 하나당 50 대 100**에서 온다. ⚠️ **갈리는 자리 하나를 구현이 가정으로 닫았다** — 「표적당 절반」이 ① 타격당 피해만 절반인지 ② 충전량 자체가 절반인지가 문서에 없다. ①로 둔다: **충전량과 수명은 그대로이고 타격당 피해만 절반**이다. 까닭은 W01 3-1 의 본전 계산이 **한 대 때릴 때의 수**(99 대 49)를 맞대고 있어서다 — ②로 두면 수명이 반이 되어 그 표가 다른 것을 재게 된다. 곁에 튀는 피해도 같은 비를 쓴다</t>
+          <t xml:space="preserve">회피 스택 상한 = 부스터 노드 대수 × 이 계수. 구 2칸 → 4칸(2026-09-17 사용자 확정) — 260917_V02 2-2 실측에서 상한 4가 필요치 50부터 이미 병목이었다. 시작 보드(부스터 둘) 상한 8</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">광역형의 대가 — 여럿을 치는 대신 하나에는 절반만 준다</t>
+          <t xml:space="preserve">로봇 생존 손잡이 — 그릇 쪽. 채우는 속도(추진제 필요 생산치)와 다른 축이다</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">260918_W01 3-1 · 플레이어블 로봇 기획서「무기 스펙트럼」</t>
+          <t xml:space="preserve">밸런스「회피와 기동 라인」· 전투「회피」· 260917_W04 2장</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">droneAoeJudgeRadius</t>
+          <t xml:space="preserve">droneAoeDamageFactor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">광역형 드론 광역 판정 반경(칸)</t>
+          <t xml:space="preserve">광역형 드론 표적당 피해 비 (🗑️ 파생 · 읽지 않음)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1416,24 +1416,24 @@
         </is>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ **잠정 점값**(2026-09-18 · 260918_W01 3장). 설계가 확정한 것은 반경이 아니라 **본전 4마리**이고, 2칸은 그 4마리를 만들 것으로 보고 넣은 추정이다(보병 유효 사거리 2.0에서 끌어왔다). 🗑️ 구 거동 폐기 — 반경 칸이 없어 **드론 사거리 9.2를 그대로** 쓰고 있었고, 그러면 화면 안 적이 사실상 전부 들어와 광역형에 대가가 없었다. 광역형 한 기의 **평균 표적 수 실측**이 나오면 그 수에 맞춰 옮긴다</t>
+          <t xml:space="preserve">🗑️🗑️ **폐기 — 좌표 `dBAoe` 50 으로 이관**(2026-09-19 · `260918_W02` 5장 문안). **값은 남기되 읽는 곳이 없다.** 이 배수는 이제 표의 좌표 둘(누적형 100 · 광역형 50)에서 **나눠서** 나온다 — 같은 값이 문서에 50, 코드에 0.5 로 두 자리에 살던 것을 한 자리로 모았다. 아래는 폐기 전 근거다. ⚠️ **가정 표기** — 사용자가 「문서대로 코드를 절반으로」로 닫았고(2026-09-18), 수는 `260918_W01` 3-1 표의 **표적 하나당 50 대 100**에서 온다. ⚠️ **갈리는 자리 하나를 구현이 가정으로 닫았다** — 「표적당 절반」이 ① 타격당 피해만 절반인지 ② 충전량 자체가 절반인지가 문서에 없다. ①로 둔다: **충전량과 수명은 그대로이고 타격당 피해만 절반**이다. 까닭은 W01 3-1 의 본전 계산이 **한 대 때릴 때의 수**(99 대 49)를 맞대고 있어서다 — ②로 두면 수명이 반이 되어 그 표가 다른 것을 재게 된다. 곁에 튀는 피해도 같은 비를 쓴다</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">광역형의 대가를 세운다 — 몇 마리를 한꺼번에 맞혀야 누적형과 본전이 되는가</t>
+          <t xml:space="preserve">광역형의 대가 — 여럿을 치는 대신 하나에는 절반만 준다</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">260918_W01 3장 · 전투 시스템 문서「드론 운용」</t>
+          <t xml:space="preserve">260918_W01 3-1 · 플레이어블 로봇 기획서「무기 스펙트럼」</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">mountDroneStackFactor</t>
+          <t xml:space="preserve">droneAoeJudgeRadius</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">드론 스택 비(탄약 대비)</t>
+          <t xml:space="preserve">광역형 드론 광역 판정 반경(칸)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1460,24 +1460,24 @@
         </is>
       </c>
       <c r="F33">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ **가정 표기** — 값 0.5는 2026-09-18 사용자 확정(「현재의 1/2」)이고, **칸만 코드에서 여기로 옮겨 왔다**(구 `MountLoad.DroneStackFactor` 코드 상수 폐기 · 지침 §3 하드코딩 금지). 로봇 B 마운트 적재량 = 슬롯 8 × 스택 10 × 이 비 = **40**. 🗑️ 구 80 폐기 — 한 판에 만충이 한 번도 안 섰다. ⚠️ 대가 — 적재량이 줄어든 만큼 태그 스킬도 약해진다(등가선 재산출 입력)</t>
+          <t xml:space="preserve">✅ **3칸 — 사용자 확정**(2026-09-19 설계 창). ⚠️ `confirmed` 는 **false 로 둔다** — 확정된 것은 **이 수**이고, 본전 몇 마리가 나오는지는 아직 안 쟀다(고리 같은 값). 🗑️ 구 2칸 폐기 — 아래는 그때의 근거다. ⚠️ **잠정 점값**(2026-09-18 · 260918_W01 3장). 설계가 확정한 것은 반경이 아니라 **본전 4마리**이고, 2칸은 그 4마리를 만들 것으로 보고 넣은 추정이다(보병 유효 사거리 2.0에서 끌어왔다). 🗑️ 구 거동 폐기 — 반경 칸이 없어 **드론 사거리 9.2를 그대로** 쓰고 있었고, 그러면 화면 안 적이 사실상 전부 들어와 광역형에 대가가 없었다. 광역형 한 기의 **평균 표적 수 실측**이 나오면 그 수에 맞춰 옮긴다</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">로봇 B의 만충을 한 판 안에 서게 한다 — 자주 터지고 약해지는 쪽</t>
+          <t xml:space="preserve">광역형의 대가를 세운다 — 몇 마리를 한꺼번에 맞혀야 누적형과 본전이 되는가</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">260918_V01 8-5 · 260918_W01 6장</t>
+          <t xml:space="preserve">260918_W01 3장 · 전투 시스템 문서「드론 운용」</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeMoveDistance</t>
+          <t xml:space="preserve">mountDroneStackFactor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">회피 이동 거리(칸)</t>
+          <t xml:space="preserve">드론 스택 비(탄약 대비)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1504,24 +1504,24 @@
         </is>
       </c>
       <c r="F34">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **1.25 칸 — 사용자 확정 2026-09-18 리허설**(구 0.5 의 2.5 배 · 「회피가 눈에 안 띈다」). 🗑️ 구 0.5(격자 반 칸) 폐기. ⚠️ 시간(0.167초)은 안 건드렸으므로 **같은 시간에 2.5 배를 간다** — 속도가 2.5 배다. 구 근거: 격자 **반 칸**(아트 픽셀 96) · 사용자 확정 2026-09-17(260917_W08 2장) — 구 「설계 가정 · 미확정」 폐기. 같은 확정 묶음의 나머지 둘은 수가 아니라 규칙이라 코드에 산다 — **방향 = 가장 가까운 적의 반대쪽을 4방향에 맞춘 것**(자동) · **곡선 = 감속형**(`DodgeMotion`)</t>
+          <t xml:space="preserve">⚠️ **가정 표기** — 값 0.5는 2026-09-18 사용자 확정(「현재의 1/2」)이고, **칸만 코드에서 여기로 옮겨 왔다**(구 `MountLoad.DroneStackFactor` 코드 상수 폐기 · 지침 §3 하드코딩 금지). 로봇 B 마운트 적재량 = 슬롯 8 × 스택 10 × 이 비 = **40**. 🗑️ 구 80 폐기 — 한 판에 만충이 한 번도 안 섰다. ⚠️ 대가 — 적재량이 줄어든 만큼 태그 스킬도 약해진다(등가선 재산출 입력)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">회피가 화면에서 보이게 — 기체가 짧게 밀려난다</t>
+          <t xml:space="preserve">로봇 B의 만충을 한 판 안에 서게 한다 — 자주 터지고 약해지는 쪽</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 시스템 문서「회피」 이동 행 · 260917_W07 3장</t>
+          <t xml:space="preserve">260918_V01 8-5 · 260918_W01 6장</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeMoveSeconds</t>
+          <t xml:space="preserve">dodgeMoveDistance</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">회피 이동 시간(초)</t>
+          <t xml:space="preserve">회피 이동 거리(칸)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1548,14 +1548,14 @@
         </is>
       </c>
       <c r="F35">
-        <v>0.167</v>
+        <v>1.25</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">**무적과 같이 시작하고 같이 끝난다**(`DodgeSystem.InvincibleSeconds` 와 같은 수). ✅ **사용자 확정 2026-09-17**(260917_W08 2장). 📌 두 값이 갈리면 무적이 끝난 뒤에도 밀리거나 그 반대가 된다 — 시험이 둘을 맞대고 있다</t>
+          <t xml:space="preserve">✅ **1.25 칸 — 사용자 확정 2026-09-18 리허설**(구 0.5 의 2.5 배 · 「회피가 눈에 안 띈다」). 🗑️ 구 0.5(격자 반 칸) 폐기. ⚠️ 시간(0.167초)은 안 건드렸으므로 **같은 시간에 2.5 배를 간다** — 속도가 2.5 배다. 구 근거: 격자 **반 칸**(아트 픽셀 96) · 사용자 확정 2026-09-17(260917_W08 2장) — 구 「설계 가정 · 미확정」 폐기. 같은 확정 묶음의 나머지 둘은 수가 아니라 규칙이라 코드에 산다 — **방향 = 가장 가까운 적의 반대쪽을 4방향에 맞춘 것**(자동) · **곡선 = 감속형**(`DodgeMotion`)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -1578,38 +1578,38 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">propellantNeed</t>
+          <t xml:space="preserve">dodgeMoveSeconds</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">추진제 필요 생산치</t>
+          <t xml:space="preserve">회피 이동 시간(초)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체·버스트</t>
+          <t xml:space="preserve">원점·곡선</t>
         </is>
       </c>
       <c r="F36">
-        <v>30</v>
+        <v>0.167</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">기초 군수 1대가 3초에 1개(노드 생산력 10 ÷ 필요 생산치 30). 구 150(15초에 1개) 폐기 — 2026-09-17 사용자 확정. 리허설에서 회피가 제대로 발동했는데도 드물어 안 보였다</t>
+          <t xml:space="preserve">**무적과 같이 시작하고 같이 끝난다**(`DodgeSystem.InvincibleSeconds` 와 같은 수). ✅ **사용자 확정 2026-09-17**(260917_W08 2장). 📌 두 값이 갈리면 무적이 끝난 뒤에도 밀리거나 그 반대가 된다 — 시험이 둘을 맞대고 있다</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">로봇 생존 손잡이 — 채우는 속도 쪽. 그릇(회피 스택 상한)과 다른 축이다</t>
+          <t xml:space="preserve">회피가 화면에서 보이게 — 기체가 짧게 밀려난다</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스「회피와 기동 라인」·「레시피와 탄종 재정의」 · 260917_W06 2장</t>
+          <t xml:space="preserve">전투 시스템 문서「회피」 이동 행 · 260917_W07 3장</t>
         </is>
       </c>
     </row>
@@ -1622,38 +1622,38 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">robotHp</t>
+          <t xml:space="preserve">propellantNeed</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">로봇 HP</t>
+          <t xml:space="preserve">추진제 필요 생산치</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">원점·곡선</t>
+          <t xml:space="preserve">합체·버스트</t>
         </is>
       </c>
       <c r="F37">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">로봇 A·B 동일. 2026-09-17 사용자 확정 — 사람이 HP 1000 으로 S1 을 넘겼다. 하네스는 같은 값에서 졌지만 하네스는 수동 회피·태그·보드 재배치를 하지 않으므로 하한선으로 읽는다</t>
+          <t xml:space="preserve">기초 군수 1대가 3초에 1개(노드 생산력 10 ÷ 필요 생산치 30). 구 150(15초에 1개) 폐기 — 2026-09-17 사용자 확정. 리허설에서 회피가 제대로 발동했는데도 드물어 안 보였다</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">생존 세 층의 맨 아래. 가운데 층(쉴드)이 채워지면 함께 다시 본다</t>
+          <t xml:space="preserve">로봇 생존 손잡이 — 채우는 속도 쪽. 그릇(회피 스택 상한)과 다른 축이다</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」· 밸런스「회피와 기동 라인」 · 260917_W05 3장</t>
+          <t xml:space="preserve">밸런스「회피와 기동 라인」·「레시피와 탄종 재정의」 · 260917_W06 2장</t>
         </is>
       </c>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">shieldMax</t>
+          <t xml:space="preserve">robotHp</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉴드 최대치</t>
+          <t xml:space="preserve">로봇 HP</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1680,24 +1680,24 @@
         </is>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">🗑️ **폐기 — 2026-09-17 사용자 결정.** 로봇에 고정으로 걸던 그릇이다. 최대치는 이제 **쉴드 발생 노드 수 × shieldMaxPerNode** 다(회피의 「부스터 × 4」와 같은 규칙). `260917_V04` 구현 판단 4(「최대치는 로봇의 것 · 노드는 속도만」)가 뒤집혔다. ⚠️ 값 0 을 그대로 둔다 — 이 칸을 읽는 곳이 남아 있으면 0 이어야 옛 규칙이 안 살아난다</t>
+          <t xml:space="preserve">로봇 A·B 동일. 2026-09-17 사용자 확정 — 사람이 HP 1000 으로 S1 을 넘겼다. 하네스는 같은 값에서 졌지만 하네스는 수동 회피·태그·보드 재배치를 하지 않으므로 하한선으로 읽는다</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">생존 세 층의 가운데 — 쉴드</t>
+          <t xml:space="preserve">생존 세 층의 맨 아래. 가운데 층(쉴드)이 채워지면 함께 다시 본다</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장</t>
+          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」· 밸런스「회피와 기동 라인」 · 260917_W05 3장</t>
         </is>
       </c>
     </row>
@@ -1710,12 +1710,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">shieldMaxPerNode</t>
+          <t xml:space="preserve">shieldMax</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉴드 발생 노드 1대당 최대치</t>
+          <t xml:space="preserve">쉴드 최대치</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1724,24 +1724,24 @@
         </is>
       </c>
       <c r="F39">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉴드 최대치 = **발생 노드 수 × 200** (2026-09-17 사용자 확정). 회피 스택 상한이 「부스터 대수 × 4」인 것과 **같은 규칙**이라 생존 두 층이 한 문법으로 읽힌다. ⚠️ **노드가 0 이면 최대치도 0** — 시작 보드에 쉴드 줄이 없으므로 배포 거동은 지금 그대로다. ⚠️ 충전률(개당 충전량)은 **아직 미정**이다</t>
+          <t xml:space="preserve">🗑️ **폐기 — 2026-09-17 사용자 결정.** 로봇에 고정으로 걸던 그릇이다. 최대치는 이제 **쉴드 발생 노드 수 × shieldMaxPerNode** 다(회피의 「부스터 × 4」와 같은 규칙). `260917_V04` 구현 판단 4(「최대치는 로봇의 것 · 노드는 속도만」)가 뒤집혔다. ⚠️ 값 0 을 그대로 둔다 — 이 칸을 읽는 곳이 남아 있으면 0 이어야 옛 규칙이 안 살아난다</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">보드가 생존을 바꾸는 고리 — 그릇도 노드가 정한다</t>
+          <t xml:space="preserve">생존 세 층의 가운데 — 쉴드</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장 · 사용자 결정 09-17</t>
+          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">shieldChargePerMaterial</t>
+          <t xml:space="preserve">shieldMaxPerNode</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉴드 재료 1개당 충전량</t>
+          <t xml:space="preserve">쉴드 발생 노드 1대당 최대치</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1768,24 +1768,24 @@
         </is>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">🗑️ 폐기 — 2026-09-17 사용자 결정. 개당 충전량을 직접 정하던 칸이다. 충전률이 **최대치의 고정 비율**이 되면서 개당 충전량은 **파생값**이 됐다 (= 최대치 × 비율 ÷ 노드 대당 재료 소비). ⚠️ 값 0 을 그대로 둔다 — 읽는 곳이 남아도 옛 규칙이 안 살아난다</t>
+          <t xml:space="preserve">쉴드 최대치 = **발생 노드 수 × 200** (2026-09-17 사용자 확정). 회피 스택 상한이 「부스터 대수 × 4」인 것과 **같은 규칙**이라 생존 두 층이 한 문법으로 읽힌다. ⚠️ **노드가 0 이면 최대치도 0** — 시작 보드에 쉴드 줄이 없으므로 배포 거동은 지금 그대로다. ⚠️ 충전률(개당 충전량)은 **아직 미정**이다</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">생존 세 층의 가운데 — 쉴드</t>
+          <t xml:space="preserve">보드가 생존을 바꾸는 고리 — 그릇도 노드가 정한다</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장</t>
+          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장 · 사용자 결정 09-17</t>
         </is>
       </c>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">shieldChargeRatioPerSec</t>
+          <t xml:space="preserve">shieldChargePerMaterial</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉴드 초당 충전 비율</t>
+          <t xml:space="preserve">쉴드 재료 1개당 충전량</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1812,24 +1812,24 @@
         </is>
       </c>
       <c r="F41">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉴드 충전률 = **최대치 × 0.025/초** (2026-09-17 사용자 확정). 노드 수와 무관한 **고정 비율**이라 빈 게이지가 차는 데 늘 **40초**다 — 노드 1대·최대치 200 이면 5/초. ⚠️ **재료 게이트는 그대로다** — 재료가 안 오면 그만큼 느려지고, 아예 없으면 안 찬다. 개당 충전량은 이제 파생값이다(최대치 × 비율 ÷ 노드 대당 소비)</t>
+          <t xml:space="preserve">🗑️ 폐기 — 2026-09-17 사용자 결정. 개당 충전량을 직접 정하던 칸이다. 충전률이 **최대치의 고정 비율**이 되면서 개당 충전량은 **파생값**이 됐다 (= 최대치 × 비율 ÷ 노드 대당 재료 소비). ⚠️ 값 0 을 그대로 둔다 — 읽는 곳이 남아도 옛 규칙이 안 살아난다</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">그릇이 커지면 채우는 데 걸리는 시간은 그대로 — 두 손잡이가 안 겹친다</t>
+          <t xml:space="preserve">생존 세 층의 가운데 — 쉴드</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 사용자 결정 09-17</t>
+          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장</t>
         </is>
       </c>
     </row>
@@ -1842,12 +1842,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">shieldMaterialPerSec</t>
+          <t xml:space="preserve">shieldChargeRatioPerSec</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉴드 발생 노드 1대의 재료 소비(개/초)</t>
+          <t xml:space="preserve">쉴드 초당 충전 비율</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1856,24 +1856,24 @@
         </is>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>0.025</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">측정용 고정값 1 — 쉴드 재료 필요 생산치가 10이라 기초 군수 1대가 1개/초를 낸다(군수 1대 = 발생 노드 1대). **확정값이 아니다**</t>
+          <t xml:space="preserve">쉴드 충전률 = **최대치 × 0.025/초** (2026-09-17 사용자 확정). 노드 수와 무관한 **고정 비율**이라 빈 게이지가 차는 데 늘 **40초**다 — 노드 1대·최대치 200 이면 5/초. ⚠️ **재료 게이트는 그대로다** — 재료가 안 오면 그만큼 느려지고, 아예 없으면 안 찬다. 개당 충전량은 이제 파생값이다(최대치 × 비율 ÷ 노드 대당 소비)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">생존 세 층의 가운데 — 쉴드</t>
+          <t xml:space="preserve">그릇이 커지면 채우는 데 걸리는 시간은 그대로 — 두 손잡이가 안 겹친다</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장</t>
+          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 사용자 결정 09-17</t>
         </is>
       </c>
     </row>
@@ -1886,38 +1886,38 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd</t>
+          <t xml:space="preserve">shieldMaterialPerSec</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체 지속(초)</t>
+          <t xml:space="preserve">쉴드 발생 노드 1대의 재료 소비(개/초)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체·버스트</t>
+          <t xml:space="preserve">원점·곡선</t>
         </is>
       </c>
       <c r="F43">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">15초=필연 밴드 협소 / 30초=만충 제약 충돌</t>
+          <t xml:space="preserve">측정용 고정값 1 — 쉴드 재료 필요 생산치가 10이라 기초 군수 1대가 1개/초를 낸다(군수 1대 = 발생 노드 1대). **확정값이 아니다**</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">예산식 지속 항 (구 '버스트 지속' 폐기 — 지속은 합체의 속성)</t>
+          <t xml:space="preserve">생존 세 층의 가운데 — 쉴드</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 5-2 (2026-07-23)</t>
+          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">gaugeFull</t>
+          <t xml:space="preserve">bd</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">게이지 만충(초)</t>
+          <t xml:space="preserve">합체 지속(초)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1944,24 +1944,24 @@
         </is>
       </c>
       <c r="F44">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">공통 게이지 1개(전투 수행 충전·스테이지당 1회) — 그리드 15×6, 제약 만충≤100초 충족</t>
+          <t xml:space="preserve">15초=필연 밴드 협소 / 30초=만충 제약 충돌</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체·버스트 동시 발동 조건</t>
+          <t xml:space="preserve">예산식 지속 항 (구 '버스트 지속' 폐기 — 지속은 합체의 속성)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 5-1 (2026-07-23)</t>
+          <t xml:space="preserve">밸런스 5-2 (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">bc</t>
+          <t xml:space="preserve">gaugeFull</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">버스트 계수 %</t>
+          <t xml:space="preserve">게이지 만충(초)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1988,24 +1988,24 @@
         </is>
       </c>
       <c r="F45">
-        <v>300</v>
+        <v>90</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">순간 1회 = 발동 순간 스냅샷 × 300% ≈ 852 — 예산 밖 마진 항</t>
+          <t xml:space="preserve">공통 게이지 1개(전투 수행 충전·스테이지당 1회) — 그리드 15×6, 제약 만충≤100초 충족</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">오프닝 필살 스파이크 (등장 특공과 동렬)</t>
+          <t xml:space="preserve">합체·버스트 동시 발동 조건</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 5-3 (2026-07-23)</t>
+          <t xml:space="preserve">밸런스 5-1 (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -2018,38 +2018,38 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrapPerKill</t>
+          <t xml:space="preserve">bc</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">마리당 고철</t>
+          <t xml:space="preserve">버스트 계수 %</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">경제(고철)</t>
+          <t xml:space="preserve">합체·버스트</t>
         </is>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">처치당 고철(TBD — 노드 가격 카탈로그와 결합 확정)</t>
+          <t xml:space="preserve">순간 1회 = 발동 순간 스냅샷 × 300% ≈ 852 — 예산 밖 마진 항</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">고철=킬 기반</t>
+          <t xml:space="preserve">오프닝 필살 스파이크 (등장 특공과 동렬)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">스테이지 기획서「파밍 규칙」</t>
+          <t xml:space="preserve">밸런스 5-3 (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">offlineHours</t>
+          <t xml:space="preserve">scrapPerKill</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">오프라인 시간(h,상한36)</t>
+          <t xml:space="preserve">마리당 고철</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2076,24 +2076,24 @@
         </is>
       </c>
       <c r="F47">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">꺼둔 시간(상한 36h만 확정)</t>
+          <t xml:space="preserve">처치당 고철(TBD — 노드 가격 카탈로그와 결합 확정)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">오프라인 창</t>
+          <t xml:space="preserve">고철=킬 기반</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">스테이지 기획서「오프라인 보상」</t>
+          <t xml:space="preserve">스테이지 기획서「파밍 규칙」</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">offlineCoef</t>
+          <t xml:space="preserve">offlineHours</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">오프라인 계수</t>
+          <t xml:space="preserve">오프라인 시간(h,상한36)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2120,19 +2120,19 @@
         </is>
       </c>
       <c r="F48">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">수입 계수(TBD 밴드 — 1 미만이어야 꺼두는 편이 이득이 되지 않음)</t>
+          <t xml:space="preserve">꺼둔 시간(상한 36h만 확정)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">수입 = 상주 스테이지 최고 파밍 시급 × min(꺼둔 시간, 36h) × 계수</t>
+          <t xml:space="preserve">오프라인 창</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">offlineBaseRate</t>
+          <t xml:space="preserve">offlineCoef</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">오프라인 기본 시급(고철/h)</t>
+          <t xml:space="preserve">오프라인 계수</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2164,22 +2164,66 @@
         </is>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
+          <t xml:space="preserve">수입 계수(TBD 밴드 — 1 미만이어야 꺼두는 편이 이득이 되지 않음)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수입 = 상주 스테이지 최고 파밍 시급 × min(꺼둔 시간, 36h) × 계수</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스테이지 기획서「오프라인 보상」</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>48</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">offlineBaseRate</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오프라인 기본 시급(고철/h)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경제(고철)</t>
+        </is>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t xml:space="preserve">상주 스테이지에 파밍 기록이 없을 때 쓰는 값(TBD). 0 = 미측정 센티넬</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">기록 없음 폴백</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">스테이지 기획서「오프라인 보상」</t>
         </is>
@@ -3009,12 +3053,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">slot</t>
+          <t xml:space="preserve">dBAoe</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">동시 출격 슬롯</t>
+          <t xml:space="preserve">드론 기당피해 — 광역형</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3023,24 +3067,24 @@
         </is>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">상수(강화 비대상 — 미결 #13)</t>
+          <t xml:space="preserve">✅ **무기 스펙트럼 좌표**(플레이어블 로봇 기획서 · 2026-07-17·07-23 확정 · 「광역형 50×2.0」). 2026-09-19 에 `droneAoeDamageFactor` 0.5 를 폐기하고 이 좌표로 모았다(`260918_W02` 5장 문안) — 종전에는 같은 값이 **문서에 50, 코드에 0.5** 로 두 자리에 살았다. ⚠️ **감쇠 규칙이 아니다** — 충전량·수명과는 다른 축이고, 「표적당 절반」은 이 좌표가 누적형 100 의 절반이라는 사실의 다른 표현일 뿐이다</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">방출 병렬도</t>
+          <t xml:space="preserve">광역형의 대가를 좌표 하나로 적는다 — 배수는 이 수를 누적형 100 으로 나눠 나온다</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">07 3장 · 밸런스 #13</t>
+          <t xml:space="preserve">260918_W02 5장 · 플레이어블 로봇 기획서「무기 스펙트럼」</t>
         </is>
       </c>
     </row>
@@ -3053,12 +3097,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">r</t>
+          <t xml:space="preserve">slot</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">방출률 r(기/초/슬롯)</t>
+          <t xml:space="preserve">동시 출격 슬롯</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3067,24 +3111,24 @@
         </is>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">min(유입 1.0, 슬롯 3×r 1.0)=1.0 실측</t>
+          <t xml:space="preserve">상수(강화 비대상 — 미결 #13)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">min(유입,슬롯×r)</t>
+          <t xml:space="preserve">방출 병렬도</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 10-3 (2026-07-23)</t>
+          <t xml:space="preserve">07 3장 · 밸런스 #13</t>
         </is>
       </c>
     </row>
@@ -3097,38 +3141,38 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">pw</t>
+          <t xml:space="preserve">r</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">노드 전력 소비(합)</t>
+          <t xml:space="preserve">방출률 r(기/초/슬롯)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">병목</t>
+          <t xml:space="preserve">로봇B 드론</t>
         </is>
       </c>
       <c r="F21">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">가동 고정비(TBD — 노드 카탈로그와 결합)</t>
+          <t xml:space="preserve">min(유입 1.0, 슬롯 3×r 1.0)=1.0 실측</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">전력=고정비 전용</t>
+          <t xml:space="preserve">min(유입,슬롯×r)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 1장</t>
+          <t xml:space="preserve">밸런스 10-3 (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -3141,12 +3185,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">pwc</t>
+          <t xml:space="preserve">pw</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">전력 공급 용량</t>
+          <t xml:space="preserve">노드 전력 소비(합)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3155,24 +3199,24 @@
         </is>
       </c>
       <c r="F22">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">발전 용량(TBD)</t>
+          <t xml:space="preserve">가동 고정비(TBD — 노드 카탈로그와 결합)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">pwc&lt;pw면 효율&lt;1</t>
+          <t xml:space="preserve">전력=고정비 전용</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 10-3</t>
+          <t xml:space="preserve">밸런스 1장</t>
         </is>
       </c>
     </row>
@@ -3185,12 +3229,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">belt</t>
+          <t xml:space="preserve">pwc</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">벨트 용량(처리량/초)</t>
+          <t xml:space="preserve">전력 공급 용량</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3199,24 +3243,24 @@
         </is>
       </c>
       <c r="F23">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">벨트 대역(TBD)</t>
+          <t xml:space="preserve">발전 용량(TBD)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">필요&lt;용량이면 무손실</t>
+          <t xml:space="preserve">pwc&lt;pw면 효율&lt;1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 6-1</t>
+          <t xml:space="preserve">밸런스 10-3</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3273,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">heat</t>
+          <t xml:space="preserve">belt</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">발열 발생/초</t>
+          <t xml:space="preserve">벨트 용량(처리량/초)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3243,19 +3287,19 @@
         </is>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">발열 합(TBD)</t>
+          <t xml:space="preserve">벨트 대역(TBD)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">임계 초과 시 감쇠</t>
+          <t xml:space="preserve">필요&lt;용량이면 무손실</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3273,12 +3317,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">heatc</t>
+          <t xml:space="preserve">heat</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">발열 임계</t>
+          <t xml:space="preserve">발열 발생/초</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3287,19 +3331,19 @@
         </is>
       </c>
       <c r="F25">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">냉각 임계(TBD)</t>
+          <t xml:space="preserve">발열 합(TBD)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">heat&gt;heatc면 감쇠</t>
+          <t xml:space="preserve">임계 초과 시 감쇠</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3317,38 +3361,38 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">store</t>
+          <t xml:space="preserve">heatc</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">저장 용량(태그 만충)</t>
+          <t xml:space="preserve">발열 임계</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">태그</t>
+          <t xml:space="preserve">병목</t>
         </is>
       </c>
       <c r="F26">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">태그 주기 10초(÷대표 생산 4발/초) · 교대 계수 0.96</t>
+          <t xml:space="preserve">냉각 임계(TBD)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">태그 주기 결정</t>
+          <t xml:space="preserve">heat&gt;heatc면 감쇠</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 4장 (2026-07-23)</t>
+          <t xml:space="preserve">밸런스 6-1</t>
         </is>
       </c>
     </row>
@@ -3361,12 +3405,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">tagspec</t>
+          <t xml:space="preserve">store</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">등장 특공(마진항)</t>
+          <t xml:space="preserve">저장 용량(태그 만충)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3375,19 +3419,19 @@
         </is>
       </c>
       <c r="F27">
-        <v>2103</v>
+        <v>40</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">식 확정: 비축 발수 × 강화 평균 발당피해 = 40×52.6</t>
+          <t xml:space="preserve">태그 주기 10초(÷대표 생산 4발/초) · 교대 계수 0.96</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">요구치 예산 밖 마진</t>
+          <t xml:space="preserve">태그 주기 결정</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3405,38 +3449,38 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">mergeMult</t>
+          <t xml:space="preserve">tagspec</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체 배율</t>
+          <t xml:space="preserve">등장 특공(마진항)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체·버스트</t>
+          <t xml:space="preserve">태그</t>
         </is>
       </c>
       <c r="F28">
-        <v>1.8</v>
+        <v>2103</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">변신 화력 = (A+B 원 DPS) × 배율 — 교대 공백 미적용</t>
+          <t xml:space="preserve">식 확정: 비축 발수 × 강화 평균 발당피해 = 40×52.6</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">예산 안 지속 항 (배율=키우기 축, 밑=물류 축)</t>
+          <t xml:space="preserve">요구치 예산 밖 마진</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 5-2 (2026-07-23)</t>
+          <t xml:space="preserve">밸런스 4장 (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -3449,12 +3493,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">mergeOutputMult</t>
+          <t xml:space="preserve">mergeMult</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체 산출량 배율</t>
+          <t xml:space="preserve">합체 배율</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3463,24 +3507,24 @@
         </is>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체 지속 중 두 보드 모든 노드의 산출량 ×2 — 재료·전력·생산 주기는 그대로, 벨트는 제외(12/초 고정). 구 표기 「생산량 200%」와 같은 값이다</t>
+          <t xml:space="preserve">변신 화력 = (A+B 원 DPS) × 배율 — 교대 공백 미적용</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체 예외 — 극적인 효과 + 두 마운트를 비우지 않게 받치는 장치</t>
+          <t xml:space="preserve">예산 안 지속 항 (배율=키우기 축, 밑=물류 축)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스「밸런스 확정 원칙」합체 예외 · 260917_W03 5장·7-2</t>
+          <t xml:space="preserve">밸런스 5-2 (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -3493,12 +3537,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeStacksPerBooster</t>
+          <t xml:space="preserve">mergeOutputMult</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">부스터 1대당 회피 스택 칸</t>
+          <t xml:space="preserve">합체 산출량 배율</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3507,24 +3551,24 @@
         </is>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">회피 스택 상한 = 부스터 노드 대수 × 이 계수. 구 2칸 → 4칸(2026-09-17 사용자 확정) — 260917_V02 2-2 실측에서 상한 4가 필요치 50부터 이미 병목이었다. 시작 보드(부스터 둘) 상한 8</t>
+          <t xml:space="preserve">합체 지속 중 두 보드 모든 노드의 산출량 ×2 — 재료·전력·생산 주기는 그대로, 벨트는 제외(12/초 고정). 구 표기 「생산량 200%」와 같은 값이다</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">로봇 생존 손잡이 — 그릇 쪽. 채우는 속도(추진제 필요 생산치)와 다른 축이다</t>
+          <t xml:space="preserve">합체 예외 — 극적인 효과 + 두 마운트를 비우지 않게 받치는 장치</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스「회피와 기동 라인」· 전투「회피」· 260917_W04 2장</t>
+          <t xml:space="preserve">밸런스「밸런스 확정 원칙」합체 예외 · 260917_W03 5장·7-2</t>
         </is>
       </c>
     </row>
@@ -3537,38 +3581,38 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">droneAoeDamageFactor</t>
+          <t xml:space="preserve">dodgeStacksPerBooster</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">광역형 드론 표적당 피해 비</t>
+          <t xml:space="preserve">부스터 1대당 회피 스택 칸</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">원점·곡선</t>
+          <t xml:space="preserve">합체·버스트</t>
         </is>
       </c>
       <c r="F31">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ **가정 표기** — 사용자가 「문서대로 코드를 절반으로」로 닫았고(2026-09-18), 수는 `260918_W01` 3-1 표의 **표적 하나당 50 대 100**에서 온다. ⚠️ **갈리는 자리 하나를 구현이 가정으로 닫았다** — 「표적당 절반」이 ① 타격당 피해만 절반인지 ② 충전량 자체가 절반인지가 문서에 없다. ①로 둔다: **충전량과 수명은 그대로이고 타격당 피해만 절반**이다. 까닭은 W01 3-1 의 본전 계산이 **한 대 때릴 때의 수**(99 대 49)를 맞대고 있어서다 — ②로 두면 수명이 반이 되어 그 표가 다른 것을 재게 된다. 곁에 튀는 피해도 같은 비를 쓴다</t>
+          <t xml:space="preserve">회피 스택 상한 = 부스터 노드 대수 × 이 계수. 구 2칸 → 4칸(2026-09-17 사용자 확정) — 260917_V02 2-2 실측에서 상한 4가 필요치 50부터 이미 병목이었다. 시작 보드(부스터 둘) 상한 8</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">광역형의 대가 — 여럿을 치는 대신 하나에는 절반만 준다</t>
+          <t xml:space="preserve">로봇 생존 손잡이 — 그릇 쪽. 채우는 속도(추진제 필요 생산치)와 다른 축이다</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">260918_W01 3-1 · 플레이어블 로봇 기획서「무기 스펙트럼」</t>
+          <t xml:space="preserve">밸런스「회피와 기동 라인」· 전투「회피」· 260917_W04 2장</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3625,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">droneAoeJudgeRadius</t>
+          <t xml:space="preserve">droneAoeDamageFactor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">광역형 드론 광역 판정 반경(칸)</t>
+          <t xml:space="preserve">광역형 드론 표적당 피해 비 (🗑️ 파생 · 읽지 않음)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3595,24 +3639,24 @@
         </is>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ **잠정 점값**(2026-09-18 · 260918_W01 3장). 설계가 확정한 것은 반경이 아니라 **본전 4마리**이고, 2칸은 그 4마리를 만들 것으로 보고 넣은 추정이다(보병 유효 사거리 2.0에서 끌어왔다). 🗑️ 구 거동 폐기 — 반경 칸이 없어 **드론 사거리 9.2를 그대로** 쓰고 있었고, 그러면 화면 안 적이 사실상 전부 들어와 광역형에 대가가 없었다. 광역형 한 기의 **평균 표적 수 실측**이 나오면 그 수에 맞춰 옮긴다</t>
+          <t xml:space="preserve">🗑️🗑️ **폐기 — 좌표 `dBAoe` 50 으로 이관**(2026-09-19 · `260918_W02` 5장 문안). **값은 남기되 읽는 곳이 없다.** 이 배수는 이제 표의 좌표 둘(누적형 100 · 광역형 50)에서 **나눠서** 나온다 — 같은 값이 문서에 50, 코드에 0.5 로 두 자리에 살던 것을 한 자리로 모았다. 아래는 폐기 전 근거다. ⚠️ **가정 표기** — 사용자가 「문서대로 코드를 절반으로」로 닫았고(2026-09-18), 수는 `260918_W01` 3-1 표의 **표적 하나당 50 대 100**에서 온다. ⚠️ **갈리는 자리 하나를 구현이 가정으로 닫았다** — 「표적당 절반」이 ① 타격당 피해만 절반인지 ② 충전량 자체가 절반인지가 문서에 없다. ①로 둔다: **충전량과 수명은 그대로이고 타격당 피해만 절반**이다. 까닭은 W01 3-1 의 본전 계산이 **한 대 때릴 때의 수**(99 대 49)를 맞대고 있어서다 — ②로 두면 수명이 반이 되어 그 표가 다른 것을 재게 된다. 곁에 튀는 피해도 같은 비를 쓴다</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">광역형의 대가를 세운다 — 몇 마리를 한꺼번에 맞혀야 누적형과 본전이 되는가</t>
+          <t xml:space="preserve">광역형의 대가 — 여럿을 치는 대신 하나에는 절반만 준다</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">260918_W01 3장 · 전투 시스템 문서「드론 운용」</t>
+          <t xml:space="preserve">260918_W01 3-1 · 플레이어블 로봇 기획서「무기 스펙트럼」</t>
         </is>
       </c>
     </row>
@@ -3625,12 +3669,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">mountDroneStackFactor</t>
+          <t xml:space="preserve">droneAoeJudgeRadius</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">드론 스택 비(탄약 대비)</t>
+          <t xml:space="preserve">광역형 드론 광역 판정 반경(칸)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3639,24 +3683,24 @@
         </is>
       </c>
       <c r="F33">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">⚠️ **가정 표기** — 값 0.5는 2026-09-18 사용자 확정(「현재의 1/2」)이고, **칸만 코드에서 여기로 옮겨 왔다**(구 `MountLoad.DroneStackFactor` 코드 상수 폐기 · 지침 §3 하드코딩 금지). 로봇 B 마운트 적재량 = 슬롯 8 × 스택 10 × 이 비 = **40**. 🗑️ 구 80 폐기 — 한 판에 만충이 한 번도 안 섰다. ⚠️ 대가 — 적재량이 줄어든 만큼 태그 스킬도 약해진다(등가선 재산출 입력)</t>
+          <t xml:space="preserve">✅ **3칸 — 사용자 확정**(2026-09-19 설계 창). ⚠️ `confirmed` 는 **false 로 둔다** — 확정된 것은 **이 수**이고, 본전 몇 마리가 나오는지는 아직 안 쟀다(고리 같은 값). 🗑️ 구 2칸 폐기 — 아래는 그때의 근거다. ⚠️ **잠정 점값**(2026-09-18 · 260918_W01 3장). 설계가 확정한 것은 반경이 아니라 **본전 4마리**이고, 2칸은 그 4마리를 만들 것으로 보고 넣은 추정이다(보병 유효 사거리 2.0에서 끌어왔다). 🗑️ 구 거동 폐기 — 반경 칸이 없어 **드론 사거리 9.2를 그대로** 쓰고 있었고, 그러면 화면 안 적이 사실상 전부 들어와 광역형에 대가가 없었다. 광역형 한 기의 **평균 표적 수 실측**이 나오면 그 수에 맞춰 옮긴다</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">로봇 B의 만충을 한 판 안에 서게 한다 — 자주 터지고 약해지는 쪽</t>
+          <t xml:space="preserve">광역형의 대가를 세운다 — 몇 마리를 한꺼번에 맞혀야 누적형과 본전이 되는가</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">260918_V01 8-5 · 260918_W01 6장</t>
+          <t xml:space="preserve">260918_W01 3장 · 전투 시스템 문서「드론 운용」</t>
         </is>
       </c>
     </row>
@@ -3669,12 +3713,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeMoveDistance</t>
+          <t xml:space="preserve">mountDroneStackFactor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">회피 이동 거리(칸)</t>
+          <t xml:space="preserve">드론 스택 비(탄약 대비)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3683,24 +3727,24 @@
         </is>
       </c>
       <c r="F34">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **1.25 칸 — 사용자 확정 2026-09-18 리허설**(구 0.5 의 2.5 배 · 「회피가 눈에 안 띈다」). 🗑️ 구 0.5(격자 반 칸) 폐기. ⚠️ 시간(0.167초)은 안 건드렸으므로 **같은 시간에 2.5 배를 간다** — 속도가 2.5 배다. 구 근거: 격자 **반 칸**(아트 픽셀 96) · 사용자 확정 2026-09-17(260917_W08 2장) — 구 「설계 가정 · 미확정」 폐기. 같은 확정 묶음의 나머지 둘은 수가 아니라 규칙이라 코드에 산다 — **방향 = 가장 가까운 적의 반대쪽을 4방향에 맞춘 것**(자동) · **곡선 = 감속형**(`DodgeMotion`)</t>
+          <t xml:space="preserve">⚠️ **가정 표기** — 값 0.5는 2026-09-18 사용자 확정(「현재의 1/2」)이고, **칸만 코드에서 여기로 옮겨 왔다**(구 `MountLoad.DroneStackFactor` 코드 상수 폐기 · 지침 §3 하드코딩 금지). 로봇 B 마운트 적재량 = 슬롯 8 × 스택 10 × 이 비 = **40**. 🗑️ 구 80 폐기 — 한 판에 만충이 한 번도 안 섰다. ⚠️ 대가 — 적재량이 줄어든 만큼 태그 스킬도 약해진다(등가선 재산출 입력)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">회피가 화면에서 보이게 — 기체가 짧게 밀려난다</t>
+          <t xml:space="preserve">로봇 B의 만충을 한 판 안에 서게 한다 — 자주 터지고 약해지는 쪽</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">전투 시스템 문서「회피」 이동 행 · 260917_W07 3장</t>
+          <t xml:space="preserve">260918_V01 8-5 · 260918_W01 6장</t>
         </is>
       </c>
     </row>
@@ -3713,12 +3757,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">dodgeMoveSeconds</t>
+          <t xml:space="preserve">dodgeMoveDistance</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">회피 이동 시간(초)</t>
+          <t xml:space="preserve">회피 이동 거리(칸)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3727,14 +3771,14 @@
         </is>
       </c>
       <c r="F35">
-        <v>0.167</v>
+        <v>1.25</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">**무적과 같이 시작하고 같이 끝난다**(`DodgeSystem.InvincibleSeconds` 와 같은 수). ✅ **사용자 확정 2026-09-17**(260917_W08 2장). 📌 두 값이 갈리면 무적이 끝난 뒤에도 밀리거나 그 반대가 된다 — 시험이 둘을 맞대고 있다</t>
+          <t xml:space="preserve">✅ **1.25 칸 — 사용자 확정 2026-09-18 리허설**(구 0.5 의 2.5 배 · 「회피가 눈에 안 띈다」). 🗑️ 구 0.5(격자 반 칸) 폐기. ⚠️ 시간(0.167초)은 안 건드렸으므로 **같은 시간에 2.5 배를 간다** — 속도가 2.5 배다. 구 근거: 격자 **반 칸**(아트 픽셀 96) · 사용자 확정 2026-09-17(260917_W08 2장) — 구 「설계 가정 · 미확정」 폐기. 같은 확정 묶음의 나머지 둘은 수가 아니라 규칙이라 코드에 산다 — **방향 = 가장 가까운 적의 반대쪽을 4방향에 맞춘 것**(자동) · **곡선 = 감속형**(`DodgeMotion`)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3757,38 +3801,38 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">propellantNeed</t>
+          <t xml:space="preserve">dodgeMoveSeconds</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">추진제 필요 생산치</t>
+          <t xml:space="preserve">회피 이동 시간(초)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체·버스트</t>
+          <t xml:space="preserve">원점·곡선</t>
         </is>
       </c>
       <c r="F36">
-        <v>30</v>
+        <v>0.167</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">기초 군수 1대가 3초에 1개(노드 생산력 10 ÷ 필요 생산치 30). 구 150(15초에 1개) 폐기 — 2026-09-17 사용자 확정. 리허설에서 회피가 제대로 발동했는데도 드물어 안 보였다</t>
+          <t xml:space="preserve">**무적과 같이 시작하고 같이 끝난다**(`DodgeSystem.InvincibleSeconds` 와 같은 수). ✅ **사용자 확정 2026-09-17**(260917_W08 2장). 📌 두 값이 갈리면 무적이 끝난 뒤에도 밀리거나 그 반대가 된다 — 시험이 둘을 맞대고 있다</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">로봇 생존 손잡이 — 채우는 속도 쪽. 그릇(회피 스택 상한)과 다른 축이다</t>
+          <t xml:space="preserve">회피가 화면에서 보이게 — 기체가 짧게 밀려난다</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스「회피와 기동 라인」·「레시피와 탄종 재정의」 · 260917_W06 2장</t>
+          <t xml:space="preserve">전투 시스템 문서「회피」 이동 행 · 260917_W07 3장</t>
         </is>
       </c>
     </row>
@@ -3801,38 +3845,38 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">robotHp</t>
+          <t xml:space="preserve">propellantNeed</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">로봇 HP</t>
+          <t xml:space="preserve">추진제 필요 생산치</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">원점·곡선</t>
+          <t xml:space="preserve">합체·버스트</t>
         </is>
       </c>
       <c r="F37">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">로봇 A·B 동일. 2026-09-17 사용자 확정 — 사람이 HP 1000 으로 S1 을 넘겼다. 하네스는 같은 값에서 졌지만 하네스는 수동 회피·태그·보드 재배치를 하지 않으므로 하한선으로 읽는다</t>
+          <t xml:space="preserve">기초 군수 1대가 3초에 1개(노드 생산력 10 ÷ 필요 생산치 30). 구 150(15초에 1개) 폐기 — 2026-09-17 사용자 확정. 리허설에서 회피가 제대로 발동했는데도 드물어 안 보였다</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">생존 세 층의 맨 아래. 가운데 층(쉴드)이 채워지면 함께 다시 본다</t>
+          <t xml:space="preserve">로봇 생존 손잡이 — 채우는 속도 쪽. 그릇(회피 스택 상한)과 다른 축이다</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」· 밸런스「회피와 기동 라인」 · 260917_W05 3장</t>
+          <t xml:space="preserve">밸런스「회피와 기동 라인」·「레시피와 탄종 재정의」 · 260917_W06 2장</t>
         </is>
       </c>
     </row>
@@ -3845,12 +3889,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">shieldMax</t>
+          <t xml:space="preserve">robotHp</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉴드 최대치</t>
+          <t xml:space="preserve">로봇 HP</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3859,24 +3903,24 @@
         </is>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">🗑️ **폐기 — 2026-09-17 사용자 결정.** 로봇에 고정으로 걸던 그릇이다. 최대치는 이제 **쉴드 발생 노드 수 × shieldMaxPerNode** 다(회피의 「부스터 × 4」와 같은 규칙). `260917_V04` 구현 판단 4(「최대치는 로봇의 것 · 노드는 속도만」)가 뒤집혔다. ⚠️ 값 0 을 그대로 둔다 — 이 칸을 읽는 곳이 남아 있으면 0 이어야 옛 규칙이 안 살아난다</t>
+          <t xml:space="preserve">로봇 A·B 동일. 2026-09-17 사용자 확정 — 사람이 HP 1000 으로 S1 을 넘겼다. 하네스는 같은 값에서 졌지만 하네스는 수동 회피·태그·보드 재배치를 하지 않으므로 하한선으로 읽는다</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">생존 세 층의 가운데 — 쉴드</t>
+          <t xml:space="preserve">생존 세 층의 맨 아래. 가운데 층(쉴드)이 채워지면 함께 다시 본다</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장</t>
+          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」· 밸런스「회피와 기동 라인」 · 260917_W05 3장</t>
         </is>
       </c>
     </row>
@@ -3889,12 +3933,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">shieldMaxPerNode</t>
+          <t xml:space="preserve">shieldMax</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉴드 발생 노드 1대당 최대치</t>
+          <t xml:space="preserve">쉴드 최대치</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3903,24 +3947,24 @@
         </is>
       </c>
       <c r="F39">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉴드 최대치 = **발생 노드 수 × 200** (2026-09-17 사용자 확정). 회피 스택 상한이 「부스터 대수 × 4」인 것과 **같은 규칙**이라 생존 두 층이 한 문법으로 읽힌다. ⚠️ **노드가 0 이면 최대치도 0** — 시작 보드에 쉴드 줄이 없으므로 배포 거동은 지금 그대로다. ⚠️ 충전률(개당 충전량)은 **아직 미정**이다</t>
+          <t xml:space="preserve">🗑️ **폐기 — 2026-09-17 사용자 결정.** 로봇에 고정으로 걸던 그릇이다. 최대치는 이제 **쉴드 발생 노드 수 × shieldMaxPerNode** 다(회피의 「부스터 × 4」와 같은 규칙). `260917_V04` 구현 판단 4(「최대치는 로봇의 것 · 노드는 속도만」)가 뒤집혔다. ⚠️ 값 0 을 그대로 둔다 — 이 칸을 읽는 곳이 남아 있으면 0 이어야 옛 규칙이 안 살아난다</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">보드가 생존을 바꾸는 고리 — 그릇도 노드가 정한다</t>
+          <t xml:space="preserve">생존 세 층의 가운데 — 쉴드</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장 · 사용자 결정 09-17</t>
+          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장</t>
         </is>
       </c>
     </row>
@@ -3933,12 +3977,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">shieldChargePerMaterial</t>
+          <t xml:space="preserve">shieldMaxPerNode</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉴드 재료 1개당 충전량</t>
+          <t xml:space="preserve">쉴드 발생 노드 1대당 최대치</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3947,24 +3991,24 @@
         </is>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">🗑️ 폐기 — 2026-09-17 사용자 결정. 개당 충전량을 직접 정하던 칸이다. 충전률이 **최대치의 고정 비율**이 되면서 개당 충전량은 **파생값**이 됐다 (= 최대치 × 비율 ÷ 노드 대당 재료 소비). ⚠️ 값 0 을 그대로 둔다 — 읽는 곳이 남아도 옛 규칙이 안 살아난다</t>
+          <t xml:space="preserve">쉴드 최대치 = **발생 노드 수 × 200** (2026-09-17 사용자 확정). 회피 스택 상한이 「부스터 대수 × 4」인 것과 **같은 규칙**이라 생존 두 층이 한 문법으로 읽힌다. ⚠️ **노드가 0 이면 최대치도 0** — 시작 보드에 쉴드 줄이 없으므로 배포 거동은 지금 그대로다. ⚠️ 충전률(개당 충전량)은 **아직 미정**이다</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">생존 세 층의 가운데 — 쉴드</t>
+          <t xml:space="preserve">보드가 생존을 바꾸는 고리 — 그릇도 노드가 정한다</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장</t>
+          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장 · 사용자 결정 09-17</t>
         </is>
       </c>
     </row>
@@ -3977,12 +4021,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">shieldChargeRatioPerSec</t>
+          <t xml:space="preserve">shieldChargePerMaterial</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉴드 초당 충전 비율</t>
+          <t xml:space="preserve">쉴드 재료 1개당 충전량</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3991,24 +4035,24 @@
         </is>
       </c>
       <c r="F41">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉴드 충전률 = **최대치 × 0.025/초** (2026-09-17 사용자 확정). 노드 수와 무관한 **고정 비율**이라 빈 게이지가 차는 데 늘 **40초**다 — 노드 1대·최대치 200 이면 5/초. ⚠️ **재료 게이트는 그대로다** — 재료가 안 오면 그만큼 느려지고, 아예 없으면 안 찬다. 개당 충전량은 이제 파생값이다(최대치 × 비율 ÷ 노드 대당 소비)</t>
+          <t xml:space="preserve">🗑️ 폐기 — 2026-09-17 사용자 결정. 개당 충전량을 직접 정하던 칸이다. 충전률이 **최대치의 고정 비율**이 되면서 개당 충전량은 **파생값**이 됐다 (= 최대치 × 비율 ÷ 노드 대당 재료 소비). ⚠️ 값 0 을 그대로 둔다 — 읽는 곳이 남아도 옛 규칙이 안 살아난다</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">그릇이 커지면 채우는 데 걸리는 시간은 그대로 — 두 손잡이가 안 겹친다</t>
+          <t xml:space="preserve">생존 세 층의 가운데 — 쉴드</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 사용자 결정 09-17</t>
+          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4065,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">shieldMaterialPerSec</t>
+          <t xml:space="preserve">shieldChargeRatioPerSec</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">쉴드 발생 노드 1대의 재료 소비(개/초)</t>
+          <t xml:space="preserve">쉴드 초당 충전 비율</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4035,24 +4079,24 @@
         </is>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>0.025</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">측정용 고정값 1 — 쉴드 재료 필요 생산치가 10이라 기초 군수 1대가 1개/초를 낸다(군수 1대 = 발생 노드 1대). **확정값이 아니다**</t>
+          <t xml:space="preserve">쉴드 충전률 = **최대치 × 0.025/초** (2026-09-17 사용자 확정). 노드 수와 무관한 **고정 비율**이라 빈 게이지가 차는 데 늘 **40초**다 — 노드 1대·최대치 200 이면 5/초. ⚠️ **재료 게이트는 그대로다** — 재료가 안 오면 그만큼 느려지고, 아예 없으면 안 찬다. 개당 충전량은 이제 파생값이다(최대치 × 비율 ÷ 노드 대당 소비)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">생존 세 층의 가운데 — 쉴드</t>
+          <t xml:space="preserve">그릇이 커지면 채우는 데 걸리는 시간은 그대로 — 두 손잡이가 안 겹친다</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장</t>
+          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 사용자 결정 09-17</t>
         </is>
       </c>
     </row>
@@ -4065,38 +4109,38 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd</t>
+          <t xml:space="preserve">shieldMaterialPerSec</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체 지속(초)</t>
+          <t xml:space="preserve">쉴드 발생 노드 1대의 재료 소비(개/초)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체·버스트</t>
+          <t xml:space="preserve">원점·곡선</t>
         </is>
       </c>
       <c r="F43">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">15초=필연 밴드 협소 / 30초=만충 제약 충돌</t>
+          <t xml:space="preserve">측정용 고정값 1 — 쉴드 재료 필요 생산치가 10이라 기초 군수 1대가 1개/초를 낸다(군수 1대 = 발생 노드 1대). **확정값이 아니다**</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">예산식 지속 항 (구 '버스트 지속' 폐기 — 지속은 합체의 속성)</t>
+          <t xml:space="preserve">생존 세 층의 가운데 — 쉴드</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 5-2 (2026-07-23)</t>
+          <t xml:space="preserve">플레이어블 로봇 기획서「생존 체계」 · 260917_W05 5장</t>
         </is>
       </c>
     </row>
@@ -4109,12 +4153,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">gaugeFull</t>
+          <t xml:space="preserve">bd</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">게이지 만충(초)</t>
+          <t xml:space="preserve">합체 지속(초)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4123,24 +4167,24 @@
         </is>
       </c>
       <c r="F44">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">공통 게이지 1개(전투 수행 충전·스테이지당 1회) — 그리드 15×6, 제약 만충≤100초 충족</t>
+          <t xml:space="preserve">15초=필연 밴드 협소 / 30초=만충 제약 충돌</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">합체·버스트 동시 발동 조건</t>
+          <t xml:space="preserve">예산식 지속 항 (구 '버스트 지속' 폐기 — 지속은 합체의 속성)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 5-1 (2026-07-23)</t>
+          <t xml:space="preserve">밸런스 5-2 (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -4153,12 +4197,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">bc</t>
+          <t xml:space="preserve">gaugeFull</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">버스트 계수 %</t>
+          <t xml:space="preserve">게이지 만충(초)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4167,24 +4211,24 @@
         </is>
       </c>
       <c r="F45">
-        <v>300</v>
+        <v>90</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">순간 1회 = 발동 순간 스냅샷 × 300% ≈ 852 — 예산 밖 마진 항</t>
+          <t xml:space="preserve">공통 게이지 1개(전투 수행 충전·스테이지당 1회) — 그리드 15×6, 제약 만충≤100초 충족</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">오프닝 필살 스파이크 (등장 특공과 동렬)</t>
+          <t xml:space="preserve">합체·버스트 동시 발동 조건</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">밸런스 5-3 (2026-07-23)</t>
+          <t xml:space="preserve">밸런스 5-1 (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -4197,38 +4241,38 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">scrapPerKill</t>
+          <t xml:space="preserve">bc</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">마리당 고철</t>
+          <t xml:space="preserve">버스트 계수 %</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">경제(고철)</t>
+          <t xml:space="preserve">합체·버스트</t>
         </is>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">처치당 고철(TBD — 노드 가격 카탈로그와 결합 확정)</t>
+          <t xml:space="preserve">순간 1회 = 발동 순간 스냅샷 × 300% ≈ 852 — 예산 밖 마진 항</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">고철=킬 기반</t>
+          <t xml:space="preserve">오프닝 필살 스파이크 (등장 특공과 동렬)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">스테이지 기획서「파밍 규칙」</t>
+          <t xml:space="preserve">밸런스 5-3 (2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4285,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">offlineHours</t>
+          <t xml:space="preserve">scrapPerKill</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">오프라인 시간(h,상한36)</t>
+          <t xml:space="preserve">마리당 고철</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4255,24 +4299,24 @@
         </is>
       </c>
       <c r="F47">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">꺼둔 시간(상한 36h만 확정)</t>
+          <t xml:space="preserve">처치당 고철(TBD — 노드 가격 카탈로그와 결합 확정)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">오프라인 창</t>
+          <t xml:space="preserve">고철=킬 기반</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">스테이지 기획서「오프라인 보상」</t>
+          <t xml:space="preserve">스테이지 기획서「파밍 규칙」</t>
         </is>
       </c>
     </row>
@@ -4285,12 +4329,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">offlineCoef</t>
+          <t xml:space="preserve">offlineHours</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">오프라인 계수</t>
+          <t xml:space="preserve">오프라인 시간(h,상한36)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4299,19 +4343,19 @@
         </is>
       </c>
       <c r="F48">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">수입 계수(TBD 밴드 — 1 미만이어야 꺼두는 편이 이득이 되지 않음)</t>
+          <t xml:space="preserve">꺼둔 시간(상한 36h만 확정)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">수입 = 상주 스테이지 최고 파밍 시급 × min(꺼둔 시간, 36h) × 계수</t>
+          <t xml:space="preserve">오프라인 창</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4329,12 +4373,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">offlineBaseRate</t>
+          <t xml:space="preserve">offlineCoef</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">오프라인 기본 시급(고철/h)</t>
+          <t xml:space="preserve">오프라인 계수</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4343,22 +4387,66 @@
         </is>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
+          <t xml:space="preserve">수입 계수(TBD 밴드 — 1 미만이어야 꺼두는 편이 이득이 되지 않음)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">수입 = 상주 스테이지 최고 파밍 시급 × min(꺼둔 시간, 36h) × 계수</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">스테이지 기획서「오프라인 보상」</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>48</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">offlineBaseRate</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">오프라인 기본 시급(고철/h)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경제(고철)</t>
+        </is>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t xml:space="preserve">상주 스테이지에 파밍 기록이 없을 때 쓰는 값(TBD). 0 = 미측정 센티넬</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">기록 없음 폴백</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t xml:space="preserve">스테이지 기획서「오프라인 보상」</t>
         </is>

--- a/Tables/BALANCE_PARAM_DATA.xlsx
+++ b/Tables/BALANCE_PARAM_DATA.xlsx
@@ -1460,14 +1460,14 @@
         </is>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **3칸 — 사용자 확정**(2026-09-19 설계 창). ⚠️ `confirmed` 는 **false 로 둔다** — 확정된 것은 **이 수**이고, 본전 몇 마리가 나오는지는 아직 안 쟀다(고리 같은 값). 🗑️ 구 2칸 폐기 — 아래는 그때의 근거다. ⚠️ **잠정 점값**(2026-09-18 · 260918_W01 3장). 설계가 확정한 것은 반경이 아니라 **본전 4마리**이고, 2칸은 그 4마리를 만들 것으로 보고 넣은 추정이다(보병 유효 사거리 2.0에서 끌어왔다). 🗑️ 구 거동 폐기 — 반경 칸이 없어 **드론 사거리 9.2를 그대로** 쓰고 있었고, 그러면 화면 안 적이 사실상 전부 들어와 광역형에 대가가 없었다. 광역형 한 기의 **평균 표적 수 실측**이 나오면 그 수에 맞춰 옮긴다</t>
+          <t xml:space="preserve">✅ **5칸 — 사용자 확정**(2026-09-21). 🗑️ 구 3칸 폐기(09-19 확정을 이틀 만에 뒤집었다). ⚠️ `confirmed` 는 **false 그대로** — 확정된 것은 이 수이고 본전 몇 마리인지는 아직 안 쟀다. ⚠️ 고리 그림은 **판정 지름 그대로**(10칸)라 화면에서 두 배로 커진다. 아래는 3칸 때의 근거다. ✅ **3칸 — 사용자 확정**(2026-09-19 설계 창). ⚠️ `confirmed` 는 **false 로 둔다** — 확정된 것은 **이 수**이고, 본전 몇 마리가 나오는지는 아직 안 쟀다(고리 같은 값). 🗑️ 구 2칸 폐기 — 아래는 그때의 근거다. ⚠️ **잠정 점값**(2026-09-18 · 260918_W01 3장). 설계가 확정한 것은 반경이 아니라 **본전 4마리**이고, 2칸은 그 4마리를 만들 것으로 보고 넣은 추정이다(보병 유효 사거리 2.0에서 끌어왔다). 🗑️ 구 거동 폐기 — 반경 칸이 없어 **드론 사거리 9.2를 그대로** 쓰고 있었고, 그러면 화면 안 적이 사실상 전부 들어와 광역형에 대가가 없었다. 광역형 한 기의 **평균 표적 수 실측**이 나오면 그 수에 맞춰 옮긴다</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3683,14 +3683,14 @@
         </is>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">✅ **3칸 — 사용자 확정**(2026-09-19 설계 창). ⚠️ `confirmed` 는 **false 로 둔다** — 확정된 것은 **이 수**이고, 본전 몇 마리가 나오는지는 아직 안 쟀다(고리 같은 값). 🗑️ 구 2칸 폐기 — 아래는 그때의 근거다. ⚠️ **잠정 점값**(2026-09-18 · 260918_W01 3장). 설계가 확정한 것은 반경이 아니라 **본전 4마리**이고, 2칸은 그 4마리를 만들 것으로 보고 넣은 추정이다(보병 유효 사거리 2.0에서 끌어왔다). 🗑️ 구 거동 폐기 — 반경 칸이 없어 **드론 사거리 9.2를 그대로** 쓰고 있었고, 그러면 화면 안 적이 사실상 전부 들어와 광역형에 대가가 없었다. 광역형 한 기의 **평균 표적 수 실측**이 나오면 그 수에 맞춰 옮긴다</t>
+          <t xml:space="preserve">✅ **5칸 — 사용자 확정**(2026-09-21). 🗑️ 구 3칸 폐기(09-19 확정을 이틀 만에 뒤집었다). ⚠️ `confirmed` 는 **false 그대로** — 확정된 것은 이 수이고 본전 몇 마리인지는 아직 안 쟀다. ⚠️ 고리 그림은 **판정 지름 그대로**(10칸)라 화면에서 두 배로 커진다. 아래는 3칸 때의 근거다. ✅ **3칸 — 사용자 확정**(2026-09-19 설계 창). ⚠️ `confirmed` 는 **false 로 둔다** — 확정된 것은 **이 수**이고, 본전 몇 마리가 나오는지는 아직 안 쟀다(고리 같은 값). 🗑️ 구 2칸 폐기 — 아래는 그때의 근거다. ⚠️ **잠정 점값**(2026-09-18 · 260918_W01 3장). 설계가 확정한 것은 반경이 아니라 **본전 4마리**이고, 2칸은 그 4마리를 만들 것으로 보고 넣은 추정이다(보병 유효 사거리 2.0에서 끌어왔다). 🗑️ 구 거동 폐기 — 반경 칸이 없어 **드론 사거리 9.2를 그대로** 쓰고 있었고, 그러면 화면 안 적이 사실상 전부 들어와 광역형에 대가가 없었다. 광역형 한 기의 **평균 표적 수 실측**이 나오면 그 수에 맞춰 옮긴다</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
